--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Goteborg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -685,22 +685,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hammarby</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -801,22 +801,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -859,22 +859,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -917,22 +917,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Orgryte</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Malmo FF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>19</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1091,40 +1091,120 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vasteras SK</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>19</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hacken</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1207,22 +1207,62 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1265,22 +1265,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14</v>
+      </c>
+      <c r="N15" t="n">
+        <v>19</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1151,25 +1151,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Halmstad</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Hacken</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>L</t>
@@ -1179,58 +1179,58 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="L13" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
         <v>9</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1240,123 +1240,203 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>1.07</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Halmstad</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Sirius</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.92</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2.53</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>14</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>19</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>

--- a/new-stats/halmstads-bk.xlsx
+++ b/new-stats/halmstads-bk.xlsx
@@ -1439,22 +1439,62 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hacken</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
